--- a/manu.xlsx
+++ b/manu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DicksonAbdul-Wahab\Desktop\NeutroProject\Groundwater\Hydrosheaf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E03D5F-3560-43BD-9FCF-2FA19489C19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A1E92B-9E21-4F1B-AE1E-E846CCCB298A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="26640" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="manu" sheetId="1" r:id="rId1"/>
@@ -20,20 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
   <si>
     <t>Sample ID</t>
   </si>
   <si>
-    <t>Water Type</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Geology</t>
-  </si>
-  <si>
     <t>X coordinate</t>
   </si>
   <si>
@@ -76,24 +67,15 @@
     <t>MKB47</t>
   </si>
   <si>
-    <t>Ca-Na-HCO3</t>
-  </si>
-  <si>
     <t>Mirigu</t>
   </si>
   <si>
-    <t>Biotite Granitoid</t>
-  </si>
-  <si>
     <t>NAB13</t>
   </si>
   <si>
     <t>Nakolo</t>
   </si>
   <si>
-    <t>Banyono</t>
-  </si>
-  <si>
     <t>BUB20</t>
   </si>
   <si>
@@ -103,27 +85,15 @@
     <t>Paga</t>
   </si>
   <si>
-    <t>Subvolcanic Rock</t>
-  </si>
-  <si>
     <t>NAB14</t>
   </si>
   <si>
-    <t>Ca-Na-HCO3-Cl</t>
-  </si>
-  <si>
     <t>GOB36</t>
   </si>
   <si>
-    <t>Na-Ca-HCO3</t>
-  </si>
-  <si>
     <t>Kulwase</t>
   </si>
   <si>
-    <t>Gomowo</t>
-  </si>
-  <si>
     <t>GOB38</t>
   </si>
   <si>
@@ -226,9 +196,6 @@
     <t>NTB29</t>
   </si>
   <si>
-    <t>Na-Ca-HCO3-Cl</t>
-  </si>
-  <si>
     <t>TBB31</t>
   </si>
   <si>
@@ -241,9 +208,6 @@
     <t>PUW40</t>
   </si>
   <si>
-    <t>S/No.</t>
-  </si>
-  <si>
     <t>Station</t>
   </si>
   <si>
@@ -260,17 +224,19 @@
   </si>
   <si>
     <t>d2H</t>
+  </si>
+  <si>
+    <t>S_No</t>
+  </si>
+  <si>
+    <t>Fe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.0000000"/>
-  </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,12 +368,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -763,11 +723,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1113,3124 +1072,2871 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="T1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="U1" t="s">
+        <v>66</v>
+      </c>
+      <c r="V1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="2">
-        <v>-1.0645783</v>
-      </c>
-      <c r="H2" s="3">
+        <v>56</v>
+      </c>
+      <c r="D2">
+        <v>-1.064578</v>
+      </c>
+      <c r="E2">
         <v>10.91264</v>
       </c>
+      <c r="F2">
+        <v>217</v>
+      </c>
+      <c r="G2">
+        <v>6.3</v>
+      </c>
+      <c r="H2">
+        <v>387</v>
+      </c>
       <c r="I2">
-        <v>217</v>
+        <v>31.8</v>
       </c>
       <c r="J2">
-        <v>6.3</v>
+        <v>193</v>
       </c>
       <c r="K2">
-        <v>387</v>
+        <v>65</v>
       </c>
       <c r="L2">
-        <v>31.8</v>
+        <v>7.7</v>
       </c>
       <c r="M2">
-        <v>193</v>
+        <v>27.2</v>
       </c>
       <c r="N2">
-        <v>65</v>
+        <v>1.83</v>
       </c>
       <c r="O2">
-        <v>7.7</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="P2">
-        <v>27.2</v>
+        <v>42.49</v>
       </c>
       <c r="Q2">
-        <v>1.83</v>
+        <v>204.96</v>
       </c>
       <c r="R2">
-        <v>0.27800000000000002</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="S2">
-        <v>42.49</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="T2">
-        <v>204.96</v>
+        <v>2.0999999999999998E-2</v>
       </c>
       <c r="U2">
-        <v>4.6399999999999997</v>
+        <v>-3.72</v>
       </c>
       <c r="V2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="W2">
-        <v>-3.72</v>
-      </c>
-      <c r="X2">
         <v>-20.85</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="2">
+        <v>56</v>
+      </c>
+      <c r="D3">
         <v>-1.0614650000000001</v>
       </c>
-      <c r="H3" s="3">
+      <c r="E3">
         <v>10.910349999999999</v>
       </c>
+      <c r="F3">
+        <v>217</v>
+      </c>
+      <c r="G3">
+        <v>6.6</v>
+      </c>
+      <c r="H3">
+        <v>313</v>
+      </c>
       <c r="I3">
-        <v>217</v>
+        <v>31.2</v>
       </c>
       <c r="J3">
-        <v>6.6</v>
+        <v>156</v>
       </c>
       <c r="K3">
-        <v>313</v>
+        <v>59.9</v>
       </c>
       <c r="L3">
-        <v>31.2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="N3">
-        <v>59.9</v>
+        <v>1.29</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="P3">
-        <v>40</v>
+        <v>12.021000000000001</v>
       </c>
       <c r="Q3">
-        <v>1.29</v>
+        <v>258.64</v>
       </c>
       <c r="R3">
-        <v>2.1000000000000001E-2</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="S3">
-        <v>12.021000000000001</v>
+        <v>4.056</v>
       </c>
       <c r="T3">
-        <v>258.64</v>
+        <v>9.9750000000000005E-2</v>
       </c>
       <c r="U3">
-        <v>2.5999999999999999E-2</v>
+        <v>-3.92</v>
       </c>
       <c r="V3">
-        <v>4.056</v>
-      </c>
-      <c r="W3">
-        <v>-3.92</v>
-      </c>
-      <c r="X3">
         <v>-21.95</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="2">
+        <v>20</v>
+      </c>
+      <c r="D4">
         <v>-1.1005069999999999</v>
       </c>
-      <c r="H4" s="3">
+      <c r="E4">
         <v>10.966100000000001</v>
       </c>
+      <c r="F4">
+        <v>226</v>
+      </c>
+      <c r="G4">
+        <v>6.7</v>
+      </c>
+      <c r="H4">
+        <v>672</v>
+      </c>
       <c r="I4">
-        <v>226</v>
+        <v>32.5</v>
       </c>
       <c r="J4">
-        <v>6.7</v>
+        <v>335</v>
       </c>
       <c r="K4">
-        <v>672</v>
+        <v>66.8</v>
       </c>
       <c r="L4">
-        <v>32.5</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="M4">
-        <v>335</v>
+        <v>59.2</v>
       </c>
       <c r="N4">
-        <v>66.8</v>
+        <v>5.34</v>
       </c>
       <c r="O4">
-        <v>18.100000000000001</v>
+        <v>2E-3</v>
       </c>
       <c r="P4">
-        <v>59.2</v>
+        <v>19.835999999999999</v>
       </c>
       <c r="Q4">
-        <v>5.34</v>
+        <v>351.36</v>
       </c>
       <c r="R4">
-        <v>2E-3</v>
+        <v>20.643999999999998</v>
       </c>
       <c r="S4">
-        <v>19.835999999999999</v>
+        <v>23.19</v>
       </c>
       <c r="T4">
-        <v>351.36</v>
+        <v>2.4E-2</v>
       </c>
       <c r="U4">
-        <v>20.643999999999998</v>
+        <v>-3.76</v>
       </c>
       <c r="V4">
-        <v>23.19</v>
-      </c>
-      <c r="W4">
-        <v>-3.76</v>
-      </c>
-      <c r="X4">
         <v>-21.95</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="2">
+        <v>20</v>
+      </c>
+      <c r="D5">
         <v>-1.09687</v>
       </c>
-      <c r="H5" s="3">
+      <c r="E5">
         <v>10.969099999999999</v>
       </c>
+      <c r="F5">
+        <v>226</v>
+      </c>
+      <c r="G5">
+        <v>6.9</v>
+      </c>
+      <c r="H5">
+        <v>506</v>
+      </c>
       <c r="I5">
-        <v>226</v>
+        <v>33.9</v>
       </c>
       <c r="J5">
-        <v>6.9</v>
+        <v>253</v>
       </c>
       <c r="K5">
-        <v>506</v>
+        <v>46.4</v>
       </c>
       <c r="L5">
-        <v>33.9</v>
+        <v>9.4</v>
       </c>
       <c r="M5">
-        <v>253</v>
+        <v>19.2</v>
       </c>
       <c r="N5">
-        <v>46.4</v>
+        <v>5.97</v>
       </c>
       <c r="O5">
-        <v>9.4</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="P5">
-        <v>19.2</v>
+        <v>10.074</v>
       </c>
       <c r="Q5">
-        <v>5.97</v>
+        <v>200.08</v>
       </c>
       <c r="R5">
-        <v>0.36799999999999999</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="S5">
-        <v>10.074</v>
+        <v>8.6969999999999992</v>
       </c>
       <c r="T5">
-        <v>200.08</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U5">
-        <v>2.1000000000000001E-2</v>
+        <v>-3.93</v>
       </c>
       <c r="V5">
-        <v>8.6969999999999992</v>
-      </c>
-      <c r="W5">
-        <v>-3.93</v>
-      </c>
-      <c r="X5">
         <v>-24.2</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="2">
+        <v>20</v>
+      </c>
+      <c r="D6">
         <v>-1.0954999999999999</v>
       </c>
-      <c r="H6" s="3">
+      <c r="E6">
         <v>10.968999999999999</v>
       </c>
+      <c r="F6">
+        <v>226</v>
+      </c>
+      <c r="G6">
+        <v>6.6</v>
+      </c>
+      <c r="H6">
+        <v>511</v>
+      </c>
       <c r="I6">
-        <v>226</v>
+        <v>33.6</v>
       </c>
       <c r="J6">
-        <v>6.6</v>
+        <v>256</v>
       </c>
       <c r="K6">
-        <v>511</v>
+        <v>46</v>
       </c>
       <c r="L6">
-        <v>33.6</v>
+        <v>9.1</v>
       </c>
       <c r="M6">
-        <v>256</v>
+        <v>32</v>
       </c>
       <c r="N6">
-        <v>46</v>
+        <v>5.39</v>
       </c>
       <c r="O6">
-        <v>9.1</v>
+        <v>2E-3</v>
       </c>
       <c r="P6">
-        <v>32</v>
+        <v>5.8049999999999997</v>
       </c>
       <c r="Q6">
-        <v>5.39</v>
+        <v>244</v>
       </c>
       <c r="R6">
-        <v>2E-3</v>
+        <v>24.253</v>
       </c>
       <c r="S6">
-        <v>5.8049999999999997</v>
+        <v>6.4359999999999999</v>
       </c>
       <c r="T6">
-        <v>244</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U6">
-        <v>24.253</v>
+        <v>-4.3499999999999996</v>
       </c>
       <c r="V6">
-        <v>6.4359999999999999</v>
-      </c>
-      <c r="W6">
-        <v>-4.3499999999999996</v>
-      </c>
-      <c r="X6">
         <v>-23.75</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="2">
+        <v>17</v>
+      </c>
+      <c r="D7">
         <v>-1.0569999999999999</v>
       </c>
-      <c r="H7" s="3">
+      <c r="E7">
         <v>10.988200000000001</v>
       </c>
+      <c r="F7">
+        <v>182</v>
+      </c>
+      <c r="G7">
+        <v>6.4</v>
+      </c>
+      <c r="H7">
+        <v>450</v>
+      </c>
       <c r="I7">
-        <v>182</v>
+        <v>34.5</v>
       </c>
       <c r="J7">
-        <v>6.4</v>
+        <v>225</v>
       </c>
       <c r="K7">
-        <v>450</v>
+        <v>60.8</v>
       </c>
       <c r="L7">
-        <v>34.5</v>
+        <v>9.1</v>
       </c>
       <c r="M7">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="N7">
-        <v>60.8</v>
+        <v>2.35</v>
       </c>
       <c r="O7">
-        <v>9.1</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="P7">
-        <v>40</v>
+        <v>6.9960000000000004</v>
       </c>
       <c r="Q7">
-        <v>2.35</v>
+        <v>287.92</v>
       </c>
       <c r="R7">
-        <v>0.72499999999999998</v>
+        <v>30.19</v>
       </c>
       <c r="S7">
-        <v>6.9960000000000004</v>
+        <v>5.3159999999999998</v>
       </c>
       <c r="T7">
-        <v>287.92</v>
+        <v>3.5249999999999997E-2</v>
       </c>
       <c r="U7">
-        <v>30.19</v>
+        <v>-3.29</v>
       </c>
       <c r="V7">
-        <v>5.3159999999999998</v>
-      </c>
-      <c r="W7">
-        <v>-3.29</v>
-      </c>
-      <c r="X7">
         <v>-19.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="2">
+        <v>17</v>
+      </c>
+      <c r="D8">
         <v>-1.0555000000000001</v>
       </c>
-      <c r="H8" s="3">
+      <c r="E8">
         <v>10.997999999999999</v>
       </c>
+      <c r="F8">
+        <v>182</v>
+      </c>
+      <c r="G8">
+        <v>7.1</v>
+      </c>
+      <c r="H8">
+        <v>457</v>
+      </c>
       <c r="I8">
-        <v>182</v>
+        <v>35</v>
       </c>
       <c r="J8">
-        <v>7.1</v>
+        <v>228</v>
       </c>
       <c r="K8">
-        <v>457</v>
+        <v>60.6</v>
       </c>
       <c r="L8">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="N8">
-        <v>60.6</v>
+        <v>3.23</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="P8">
-        <v>32</v>
+        <v>2.9039999999999999</v>
       </c>
       <c r="Q8">
-        <v>3.23</v>
+        <v>283.04000000000002</v>
       </c>
       <c r="R8">
-        <v>0.39800000000000002</v>
+        <v>3.9790000000000001</v>
       </c>
       <c r="S8">
-        <v>2.9039999999999999</v>
+        <v>6.07</v>
       </c>
       <c r="T8">
-        <v>283.04000000000002</v>
+        <v>0.16499999999999998</v>
       </c>
       <c r="U8">
-        <v>3.9790000000000001</v>
+        <v>-3.39</v>
       </c>
       <c r="V8">
-        <v>6.07</v>
-      </c>
-      <c r="W8">
-        <v>-3.39</v>
-      </c>
-      <c r="X8">
         <v>-22.7</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="2">
+        <v>17</v>
+      </c>
+      <c r="D9">
         <v>-1.0559799999999999</v>
       </c>
-      <c r="H9" s="3">
+      <c r="E9">
         <v>11.00019</v>
       </c>
+      <c r="F9">
+        <v>182</v>
+      </c>
+      <c r="G9">
+        <v>6.8</v>
+      </c>
+      <c r="H9">
+        <v>308</v>
+      </c>
       <c r="I9">
-        <v>182</v>
+        <v>31.4</v>
       </c>
       <c r="J9">
-        <v>6.8</v>
+        <v>154</v>
       </c>
       <c r="K9">
-        <v>308</v>
+        <v>41.7</v>
       </c>
       <c r="L9">
-        <v>31.4</v>
+        <v>3.9</v>
       </c>
       <c r="M9">
-        <v>154</v>
+        <v>30.4</v>
       </c>
       <c r="N9">
-        <v>41.7</v>
+        <v>1.36</v>
       </c>
       <c r="O9">
-        <v>3.9</v>
+        <v>0.28699999999999998</v>
       </c>
       <c r="P9">
-        <v>30.4</v>
+        <v>9.8480000000000008</v>
       </c>
       <c r="Q9">
-        <v>1.36</v>
+        <v>165.92</v>
       </c>
       <c r="R9">
-        <v>0.28699999999999998</v>
+        <v>36.457000000000001</v>
       </c>
       <c r="S9">
-        <v>9.8480000000000008</v>
+        <v>10.409000000000001</v>
       </c>
       <c r="T9">
-        <v>165.92</v>
+        <v>2.5500000000000002E-2</v>
       </c>
       <c r="U9">
-        <v>36.457000000000001</v>
+        <v>-3.47</v>
       </c>
       <c r="V9">
-        <v>10.409000000000001</v>
-      </c>
-      <c r="W9">
-        <v>-3.47</v>
-      </c>
-      <c r="X9">
         <v>-18.7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="2">
+        <v>17</v>
+      </c>
+      <c r="D10">
         <v>-1.0510699999999999</v>
       </c>
-      <c r="H10" s="3">
+      <c r="E10">
         <v>10.996</v>
       </c>
+      <c r="F10">
+        <v>182</v>
+      </c>
+      <c r="G10">
+        <v>6.7</v>
+      </c>
+      <c r="H10">
+        <v>450</v>
+      </c>
       <c r="I10">
-        <v>182</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="J10">
-        <v>6.7</v>
+        <v>225</v>
       </c>
       <c r="K10">
-        <v>450</v>
+        <v>168</v>
       </c>
       <c r="L10">
-        <v>32.299999999999997</v>
+        <v>12.1</v>
       </c>
       <c r="M10">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="N10">
-        <v>168</v>
+        <v>2.8</v>
       </c>
       <c r="O10">
-        <v>12.1</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="P10">
-        <v>40</v>
+        <v>32.933999999999997</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>512.4</v>
       </c>
       <c r="R10">
-        <v>3.5000000000000003E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="S10">
-        <v>32.933999999999997</v>
+        <v>2.093</v>
       </c>
       <c r="T10">
-        <v>512.4</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="U10">
-        <v>1.2E-2</v>
+        <v>-3.47</v>
       </c>
       <c r="V10">
-        <v>2.093</v>
-      </c>
-      <c r="W10">
-        <v>-3.47</v>
-      </c>
-      <c r="X10">
         <v>-22.8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="2">
+        <v>17</v>
+      </c>
+      <c r="D11">
         <v>-1.0422</v>
       </c>
-      <c r="H11" s="3">
+      <c r="E11">
         <v>10.982799999999999</v>
       </c>
+      <c r="F11">
+        <v>182</v>
+      </c>
+      <c r="G11">
+        <v>6.8</v>
+      </c>
+      <c r="H11">
+        <v>335</v>
+      </c>
       <c r="I11">
-        <v>182</v>
+        <v>31.3</v>
       </c>
       <c r="J11">
-        <v>6.8</v>
+        <v>168</v>
       </c>
       <c r="K11">
-        <v>335</v>
+        <v>57.5</v>
       </c>
       <c r="L11">
-        <v>31.3</v>
+        <v>8.9</v>
       </c>
       <c r="M11">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="N11">
-        <v>57.5</v>
+        <v>2.76</v>
       </c>
       <c r="O11">
-        <v>8.9</v>
+        <v>1.4690000000000001</v>
       </c>
       <c r="P11">
-        <v>32</v>
+        <v>6.2679999999999998</v>
       </c>
       <c r="Q11">
-        <v>2.76</v>
+        <v>263.52</v>
       </c>
       <c r="R11">
-        <v>1.4690000000000001</v>
+        <v>11.207000000000001</v>
       </c>
       <c r="S11">
-        <v>6.2679999999999998</v>
+        <v>3.91</v>
       </c>
       <c r="T11">
-        <v>263.52</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U11">
-        <v>11.207000000000001</v>
+        <v>-4.03</v>
       </c>
       <c r="V11">
-        <v>3.91</v>
-      </c>
-      <c r="W11">
-        <v>-4.03</v>
-      </c>
-      <c r="X11">
         <v>-22.5</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="2">
+        <v>17</v>
+      </c>
+      <c r="D12">
         <v>-1.0407900000000001</v>
       </c>
-      <c r="H12" s="3">
+      <c r="E12">
         <v>10.979900000000001</v>
       </c>
+      <c r="F12">
+        <v>182</v>
+      </c>
+      <c r="G12">
+        <v>6.8</v>
+      </c>
+      <c r="H12">
+        <v>506</v>
+      </c>
       <c r="I12">
-        <v>182</v>
+        <v>32.9</v>
       </c>
       <c r="J12">
-        <v>6.8</v>
+        <v>253</v>
       </c>
       <c r="K12">
-        <v>506</v>
+        <v>37.1</v>
       </c>
       <c r="L12">
-        <v>32.9</v>
+        <v>7.4</v>
       </c>
       <c r="M12">
-        <v>253</v>
+        <v>38.4</v>
       </c>
       <c r="N12">
-        <v>37.1</v>
+        <v>3.79</v>
       </c>
       <c r="O12">
-        <v>7.4</v>
+        <v>2.1739999999999999</v>
       </c>
       <c r="P12">
-        <v>38.4</v>
+        <v>19.766999999999999</v>
       </c>
       <c r="Q12">
-        <v>3.79</v>
+        <v>185.44</v>
       </c>
       <c r="R12">
-        <v>2.1739999999999999</v>
+        <v>27.64</v>
       </c>
       <c r="S12">
-        <v>19.766999999999999</v>
+        <v>16.018999999999998</v>
       </c>
       <c r="T12">
-        <v>185.44</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U12">
-        <v>27.64</v>
+        <v>-3.53</v>
       </c>
       <c r="V12">
-        <v>16.018999999999998</v>
-      </c>
-      <c r="W12">
-        <v>-3.53</v>
-      </c>
-      <c r="X12">
         <v>-22.75</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="2">
+        <v>17</v>
+      </c>
+      <c r="D13">
         <v>-1.03668</v>
       </c>
-      <c r="H13" s="3">
+      <c r="E13">
         <v>10.9871</v>
       </c>
+      <c r="F13">
+        <v>182</v>
+      </c>
+      <c r="G13">
+        <v>6.7</v>
+      </c>
+      <c r="H13">
+        <v>232</v>
+      </c>
       <c r="I13">
-        <v>182</v>
+        <v>31.3</v>
       </c>
       <c r="J13">
-        <v>6.7</v>
+        <v>116</v>
       </c>
       <c r="K13">
-        <v>232</v>
+        <v>18.7</v>
       </c>
       <c r="L13">
-        <v>31.3</v>
+        <v>13.8</v>
       </c>
       <c r="M13">
-        <v>116</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="N13">
-        <v>18.7</v>
+        <v>0.95</v>
       </c>
       <c r="O13">
-        <v>13.8</v>
+        <v>1.6</v>
       </c>
       <c r="P13">
-        <v>17.600000000000001</v>
+        <v>16.128</v>
       </c>
       <c r="Q13">
-        <v>0.95</v>
+        <v>92.72</v>
       </c>
       <c r="R13">
-        <v>1.6</v>
+        <v>22.061</v>
       </c>
       <c r="S13">
-        <v>16.128</v>
+        <v>6.3E-2</v>
       </c>
       <c r="T13">
-        <v>92.72</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U13">
-        <v>22.061</v>
+        <v>-4.2</v>
       </c>
       <c r="V13">
-        <v>6.3E-2</v>
-      </c>
-      <c r="W13">
-        <v>-4.2</v>
-      </c>
-      <c r="X13">
         <v>-25.65</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="2">
+        <v>17</v>
+      </c>
+      <c r="D14">
         <v>-1.0352600000000001</v>
       </c>
-      <c r="H14" s="3">
+      <c r="E14">
         <v>10.9961</v>
       </c>
+      <c r="F14">
+        <v>182</v>
+      </c>
+      <c r="G14">
+        <v>7.1</v>
+      </c>
+      <c r="H14">
+        <v>388</v>
+      </c>
       <c r="I14">
-        <v>182</v>
+        <v>31.7</v>
       </c>
       <c r="J14">
-        <v>7.1</v>
+        <v>194</v>
       </c>
       <c r="K14">
-        <v>388</v>
+        <v>42.4</v>
       </c>
       <c r="L14">
-        <v>31.7</v>
+        <v>8.5</v>
       </c>
       <c r="M14">
-        <v>194</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="N14">
-        <v>42.4</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
-        <v>8.5</v>
+        <v>0.58599999999999997</v>
       </c>
       <c r="P14">
-        <v>35.200000000000003</v>
+        <v>3.3639999999999999</v>
       </c>
       <c r="Q14">
-        <v>1.95</v>
+        <v>190.32</v>
       </c>
       <c r="R14">
-        <v>0.58599999999999997</v>
+        <v>26.009</v>
       </c>
       <c r="S14">
-        <v>3.3639999999999999</v>
+        <v>32.463000000000001</v>
       </c>
       <c r="T14">
-        <v>190.32</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U14">
-        <v>26.009</v>
+        <v>-4.2300000000000004</v>
       </c>
       <c r="V14">
-        <v>32.463000000000001</v>
-      </c>
-      <c r="W14">
-        <v>-4.2300000000000004</v>
-      </c>
-      <c r="X14">
         <v>-22.2</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="2">
+        <v>20</v>
+      </c>
+      <c r="D15">
         <v>-1.1109500000000001</v>
       </c>
-      <c r="H15" s="3">
+      <c r="E15">
         <v>10.991860000000001</v>
       </c>
+      <c r="F15">
+        <v>226</v>
+      </c>
+      <c r="G15">
+        <v>6.7</v>
+      </c>
+      <c r="H15">
+        <v>535</v>
+      </c>
       <c r="I15">
-        <v>226</v>
+        <v>30.3</v>
       </c>
       <c r="J15">
-        <v>6.7</v>
+        <v>267</v>
       </c>
       <c r="K15">
-        <v>535</v>
+        <v>82.1</v>
       </c>
       <c r="L15">
-        <v>30.3</v>
+        <v>3.5</v>
       </c>
       <c r="M15">
-        <v>267</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="N15">
-        <v>82.1</v>
+        <v>3.49</v>
       </c>
       <c r="O15">
-        <v>3.5</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="P15">
-        <v>36.799999999999997</v>
+        <v>25.178999999999998</v>
       </c>
       <c r="Q15">
-        <v>3.49</v>
+        <v>278.16000000000003</v>
       </c>
       <c r="R15">
-        <v>0.82499999999999996</v>
+        <v>8.5030000000000001</v>
       </c>
       <c r="S15">
-        <v>25.178999999999998</v>
+        <v>6.75</v>
       </c>
       <c r="T15">
-        <v>278.16000000000003</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U15">
-        <v>8.5030000000000001</v>
+        <v>-3.94</v>
       </c>
       <c r="V15">
-        <v>6.75</v>
-      </c>
-      <c r="W15">
-        <v>-3.94</v>
-      </c>
-      <c r="X15">
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="2">
+        <v>20</v>
+      </c>
+      <c r="D16">
         <v>-1.0991599999999999</v>
       </c>
-      <c r="H16" s="3">
+      <c r="E16">
         <v>10.960140000000001</v>
       </c>
+      <c r="F16">
+        <v>226</v>
+      </c>
+      <c r="G16">
+        <v>6.8</v>
+      </c>
+      <c r="H16">
+        <v>479</v>
+      </c>
       <c r="I16">
-        <v>226</v>
+        <v>30.8</v>
       </c>
       <c r="J16">
-        <v>6.8</v>
+        <v>239</v>
       </c>
       <c r="K16">
-        <v>479</v>
+        <v>50.5</v>
       </c>
       <c r="L16">
-        <v>30.8</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="M16">
-        <v>239</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="N16">
-        <v>50.5</v>
+        <v>3.78</v>
       </c>
       <c r="O16">
-        <v>8.6999999999999993</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="P16">
-        <v>40.799999999999997</v>
+        <v>17.600999999999999</v>
       </c>
       <c r="Q16">
-        <v>3.78</v>
+        <v>244</v>
       </c>
       <c r="R16">
-        <v>0.24099999999999999</v>
+        <v>27.861000000000001</v>
       </c>
       <c r="S16">
-        <v>17.600999999999999</v>
+        <v>13.589</v>
       </c>
       <c r="T16">
-        <v>244</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U16">
-        <v>27.861000000000001</v>
+        <v>-3.65</v>
       </c>
       <c r="V16">
-        <v>13.589</v>
-      </c>
-      <c r="W16">
-        <v>-3.65</v>
-      </c>
-      <c r="X16">
         <v>-19.399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="2">
+        <v>17</v>
+      </c>
+      <c r="D17">
         <v>-1.0547</v>
       </c>
-      <c r="H17" s="3">
+      <c r="E17">
         <v>10.96602</v>
       </c>
+      <c r="F17">
+        <v>182</v>
+      </c>
+      <c r="G17">
+        <v>6.7</v>
+      </c>
+      <c r="H17">
+        <v>331</v>
+      </c>
       <c r="I17">
-        <v>182</v>
+        <v>31.5</v>
       </c>
       <c r="J17">
-        <v>6.7</v>
+        <v>165</v>
       </c>
       <c r="K17">
-        <v>331</v>
+        <v>36.9</v>
       </c>
       <c r="L17">
-        <v>31.5</v>
+        <v>8.1</v>
       </c>
       <c r="M17">
-        <v>165</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="N17">
-        <v>36.9</v>
+        <v>0.99</v>
       </c>
       <c r="O17">
-        <v>8.1</v>
+        <v>1.171</v>
       </c>
       <c r="P17">
-        <v>36.799999999999997</v>
+        <v>16.291</v>
       </c>
       <c r="Q17">
-        <v>0.99</v>
+        <v>180.56</v>
       </c>
       <c r="R17">
-        <v>1.171</v>
+        <v>34.292000000000002</v>
       </c>
       <c r="S17">
-        <v>16.291</v>
+        <v>5.37</v>
       </c>
       <c r="T17">
-        <v>180.56</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U17">
-        <v>34.292000000000002</v>
+        <v>-3.96</v>
       </c>
       <c r="V17">
-        <v>5.37</v>
-      </c>
-      <c r="W17">
-        <v>-3.96</v>
-      </c>
-      <c r="X17">
         <v>-22.9</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="2">
+        <v>17</v>
+      </c>
+      <c r="D18">
         <v>-1.0491299999999999</v>
       </c>
-      <c r="H18" s="3">
+      <c r="E18">
         <v>10.9663</v>
       </c>
+      <c r="F18">
+        <v>182</v>
+      </c>
+      <c r="G18">
+        <v>6.7</v>
+      </c>
+      <c r="H18">
+        <v>441</v>
+      </c>
       <c r="I18">
-        <v>182</v>
+        <v>29.5</v>
       </c>
       <c r="J18">
-        <v>6.7</v>
+        <v>221</v>
       </c>
       <c r="K18">
-        <v>441</v>
+        <v>59.3</v>
       </c>
       <c r="L18">
-        <v>29.5</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="M18">
-        <v>221</v>
+        <v>44</v>
       </c>
       <c r="N18">
-        <v>59.3</v>
+        <v>0.72</v>
       </c>
       <c r="O18">
-        <v>17.100000000000001</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="P18">
-        <v>44</v>
+        <v>8.0839999999999996</v>
       </c>
       <c r="Q18">
-        <v>0.72</v>
+        <v>258.64</v>
       </c>
       <c r="R18">
-        <v>4.4999999999999998E-2</v>
+        <v>19.268000000000001</v>
       </c>
       <c r="S18">
-        <v>8.0839999999999996</v>
+        <v>17.291</v>
       </c>
       <c r="T18">
-        <v>258.64</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U18">
-        <v>19.268000000000001</v>
+        <v>-3.96</v>
       </c>
       <c r="V18">
-        <v>17.291</v>
-      </c>
-      <c r="W18">
-        <v>-3.96</v>
-      </c>
-      <c r="X18">
         <v>-18.7</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="2">
+        <v>17</v>
+      </c>
+      <c r="D19">
         <v>-1.0463</v>
       </c>
-      <c r="H19" s="3">
+      <c r="E19">
         <v>10.963200000000001</v>
       </c>
+      <c r="F19">
+        <v>182</v>
+      </c>
+      <c r="G19">
+        <v>6.8</v>
+      </c>
+      <c r="H19">
+        <v>321</v>
+      </c>
       <c r="I19">
-        <v>182</v>
+        <v>32.4</v>
       </c>
       <c r="J19">
-        <v>6.8</v>
+        <v>160</v>
       </c>
       <c r="K19">
-        <v>321</v>
+        <v>50.4</v>
       </c>
       <c r="L19">
-        <v>32.4</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M19">
-        <v>160</v>
+        <v>28.8</v>
       </c>
       <c r="N19">
-        <v>50.4</v>
+        <v>1.68</v>
       </c>
       <c r="O19">
-        <v>9.3000000000000007</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="P19">
-        <v>28.8</v>
+        <v>12.79</v>
       </c>
       <c r="Q19">
-        <v>1.68</v>
+        <v>214.72</v>
       </c>
       <c r="R19">
-        <v>0.17899999999999999</v>
+        <v>29.286000000000001</v>
       </c>
       <c r="S19">
-        <v>12.79</v>
+        <v>3.0630000000000002</v>
       </c>
       <c r="T19">
-        <v>214.72</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U19">
-        <v>29.286000000000001</v>
+        <v>-3.52</v>
       </c>
       <c r="V19">
-        <v>3.0630000000000002</v>
-      </c>
-      <c r="W19">
-        <v>-3.52</v>
-      </c>
-      <c r="X19">
         <v>-21.8</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="2">
+        <v>17</v>
+      </c>
+      <c r="D20">
         <v>-1.0442400000000001</v>
       </c>
-      <c r="H20" s="3">
+      <c r="E20">
         <v>10.955870000000001</v>
       </c>
+      <c r="F20">
+        <v>182</v>
+      </c>
+      <c r="G20">
+        <v>6.6</v>
+      </c>
+      <c r="H20">
+        <v>358</v>
+      </c>
       <c r="I20">
-        <v>182</v>
+        <v>32.4</v>
       </c>
       <c r="J20">
-        <v>6.6</v>
+        <v>178</v>
       </c>
       <c r="K20">
-        <v>358</v>
+        <v>56.6</v>
       </c>
       <c r="L20">
-        <v>32.4</v>
+        <v>9.9</v>
       </c>
       <c r="M20">
-        <v>178</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="N20">
-        <v>56.6</v>
+        <v>1.45</v>
       </c>
       <c r="O20">
-        <v>9.9</v>
+        <v>2.069</v>
       </c>
       <c r="P20">
-        <v>35.200000000000003</v>
+        <v>5.7240000000000002</v>
       </c>
       <c r="Q20">
-        <v>1.45</v>
+        <v>273.27999999999997</v>
       </c>
       <c r="R20">
-        <v>2.069</v>
+        <v>10.395</v>
       </c>
       <c r="S20">
-        <v>5.7240000000000002</v>
+        <v>8.6709999999999994</v>
       </c>
       <c r="T20">
-        <v>273.27999999999997</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U20">
-        <v>10.395</v>
+        <v>0.64</v>
       </c>
       <c r="V20">
-        <v>8.6709999999999994</v>
-      </c>
-      <c r="W20">
-        <v>0.64</v>
-      </c>
-      <c r="X20">
         <v>-4.2</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="2">
+        <v>17</v>
+      </c>
+      <c r="D21">
         <v>-1.02729</v>
       </c>
-      <c r="H21" s="3">
+      <c r="E21">
         <v>10.9834</v>
       </c>
+      <c r="F21">
+        <v>182</v>
+      </c>
+      <c r="G21">
+        <v>7.1</v>
+      </c>
+      <c r="H21">
+        <v>363</v>
+      </c>
       <c r="I21">
+        <v>32</v>
+      </c>
+      <c r="J21">
         <v>182</v>
       </c>
-      <c r="J21">
-        <v>7.1</v>
-      </c>
       <c r="K21">
-        <v>363</v>
+        <v>48.5</v>
       </c>
       <c r="L21">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="M21">
-        <v>182</v>
+        <v>28.8</v>
       </c>
       <c r="N21">
-        <v>48.5</v>
+        <v>1.59</v>
       </c>
       <c r="O21">
-        <v>7.8</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="P21">
-        <v>28.8</v>
+        <v>30.164000000000001</v>
       </c>
       <c r="Q21">
-        <v>1.59</v>
+        <v>190.32</v>
       </c>
       <c r="R21">
-        <v>3.5000000000000003E-2</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="S21">
-        <v>30.164000000000001</v>
+        <v>2.1890000000000001</v>
       </c>
       <c r="T21">
-        <v>190.32</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U21">
-        <v>0.94699999999999995</v>
+        <v>-3.58</v>
       </c>
       <c r="V21">
-        <v>2.1890000000000001</v>
-      </c>
-      <c r="W21">
-        <v>-3.58</v>
-      </c>
-      <c r="X21">
         <v>-17.95</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="2">
+        <v>17</v>
+      </c>
+      <c r="D22">
         <v>-1.0236400000000001</v>
       </c>
-      <c r="H22" s="3">
+      <c r="E22">
         <v>10.9739</v>
       </c>
+      <c r="F22">
+        <v>182</v>
+      </c>
+      <c r="G22">
+        <v>6.8</v>
+      </c>
+      <c r="H22">
+        <v>352</v>
+      </c>
       <c r="I22">
-        <v>182</v>
+        <v>31.5</v>
       </c>
       <c r="J22">
-        <v>6.8</v>
+        <v>176</v>
       </c>
       <c r="K22">
-        <v>352</v>
+        <v>82.1</v>
       </c>
       <c r="L22">
-        <v>31.5</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>176</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="N22">
-        <v>82.1</v>
+        <v>0.99</v>
       </c>
       <c r="O22">
-        <v>6</v>
+        <v>1E-3</v>
       </c>
       <c r="P22">
-        <v>35.200000000000003</v>
+        <v>11.779</v>
       </c>
       <c r="Q22">
-        <v>0.99</v>
+        <v>341.6</v>
       </c>
       <c r="R22">
-        <v>1E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="S22">
-        <v>11.779</v>
+        <v>2E-3</v>
       </c>
       <c r="T22">
-        <v>341.6</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U22">
-        <v>4.0000000000000001E-3</v>
+        <v>-4.07</v>
       </c>
       <c r="V22">
-        <v>2E-3</v>
-      </c>
-      <c r="W22">
-        <v>-4.07</v>
-      </c>
-      <c r="X22">
         <v>-22.95</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="2">
+        <v>17</v>
+      </c>
+      <c r="D23">
         <v>-1.02247</v>
       </c>
-      <c r="H23" s="3">
+      <c r="E23">
         <v>10.97968</v>
       </c>
+      <c r="F23">
+        <v>182</v>
+      </c>
+      <c r="G23">
+        <v>6.7</v>
+      </c>
+      <c r="H23">
+        <v>350</v>
+      </c>
       <c r="I23">
-        <v>182</v>
+        <v>33.1</v>
       </c>
       <c r="J23">
-        <v>6.7</v>
+        <v>175</v>
       </c>
       <c r="K23">
-        <v>350</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="L23">
-        <v>33.1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>175</v>
+        <v>30.4</v>
       </c>
       <c r="N23">
-        <v>65.099999999999994</v>
+        <v>1.8</v>
       </c>
       <c r="O23">
-        <v>5</v>
+        <v>0.105</v>
       </c>
       <c r="P23">
-        <v>30.4</v>
+        <v>36.048999999999999</v>
       </c>
       <c r="Q23">
-        <v>1.8</v>
+        <v>234.24</v>
       </c>
       <c r="R23">
-        <v>0.105</v>
+        <v>1.048</v>
       </c>
       <c r="S23">
-        <v>36.048999999999999</v>
+        <v>2.1789999999999998</v>
       </c>
       <c r="T23">
-        <v>234.24</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="U23">
-        <v>1.048</v>
+        <v>-3.95</v>
       </c>
       <c r="V23">
-        <v>2.1789999999999998</v>
-      </c>
-      <c r="W23">
-        <v>-3.95</v>
-      </c>
-      <c r="X23">
         <v>-22.15</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="2">
+        <v>17</v>
+      </c>
+      <c r="D24">
         <v>-1.0170630000000001</v>
       </c>
-      <c r="H24" s="3">
+      <c r="E24">
         <v>10.9739</v>
       </c>
+      <c r="F24">
+        <v>182</v>
+      </c>
+      <c r="G24">
+        <v>7.1</v>
+      </c>
+      <c r="H24">
+        <v>308</v>
+      </c>
       <c r="I24">
-        <v>182</v>
+        <v>31.9</v>
       </c>
       <c r="J24">
-        <v>7.1</v>
+        <v>154</v>
       </c>
       <c r="K24">
-        <v>308</v>
+        <v>47.5</v>
       </c>
       <c r="L24">
-        <v>31.9</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>154</v>
+        <v>28.8</v>
       </c>
       <c r="N24">
-        <v>47.5</v>
+        <v>1.57</v>
       </c>
       <c r="O24">
-        <v>7</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="P24">
-        <v>28.8</v>
+        <v>23.8</v>
       </c>
       <c r="Q24">
-        <v>1.57</v>
+        <v>200.08</v>
       </c>
       <c r="R24">
-        <v>0.21299999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
       <c r="S24">
-        <v>23.8</v>
+        <v>3.6819999999999999</v>
       </c>
       <c r="T24">
-        <v>200.08</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U24">
-        <v>1.0469999999999999</v>
+        <v>-4.0999999999999996</v>
       </c>
       <c r="V24">
-        <v>3.6819999999999999</v>
-      </c>
-      <c r="W24">
-        <v>-4.0999999999999996</v>
-      </c>
-      <c r="X24">
         <v>-22.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="2">
+        <v>17</v>
+      </c>
+      <c r="D25">
         <v>-1.011792</v>
       </c>
-      <c r="H25" s="3">
+      <c r="E25">
         <v>10.9777</v>
       </c>
+      <c r="F25">
+        <v>182</v>
+      </c>
+      <c r="G25">
+        <v>7.3</v>
+      </c>
+      <c r="H25">
+        <v>424</v>
+      </c>
       <c r="I25">
-        <v>182</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="J25">
-        <v>7.3</v>
+        <v>212</v>
       </c>
       <c r="K25">
-        <v>424</v>
+        <v>58.1</v>
       </c>
       <c r="L25">
-        <v>32.200000000000003</v>
+        <v>12.2</v>
       </c>
       <c r="M25">
-        <v>212</v>
+        <v>42.4</v>
       </c>
       <c r="N25">
-        <v>58.1</v>
+        <v>2.42</v>
       </c>
       <c r="O25">
-        <v>12.2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="P25">
-        <v>42.4</v>
+        <v>37.917999999999999</v>
       </c>
       <c r="Q25">
-        <v>2.42</v>
+        <v>219.6</v>
       </c>
       <c r="R25">
-        <v>3.5999999999999997E-2</v>
+        <v>27.012</v>
       </c>
       <c r="S25">
-        <v>37.917999999999999</v>
+        <v>1.9890000000000001</v>
       </c>
       <c r="T25">
-        <v>219.6</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U25">
-        <v>27.012</v>
+        <v>-4.32</v>
       </c>
       <c r="V25">
-        <v>1.9890000000000001</v>
-      </c>
-      <c r="W25">
-        <v>-4.32</v>
-      </c>
-      <c r="X25">
         <v>-23.6</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="2">
+        <v>17</v>
+      </c>
+      <c r="D26">
         <v>-1.009368</v>
       </c>
-      <c r="H26" s="3">
+      <c r="E26">
         <v>10.974489999999999</v>
       </c>
+      <c r="F26">
+        <v>182</v>
+      </c>
+      <c r="G26">
+        <v>6.9</v>
+      </c>
+      <c r="H26">
+        <v>230</v>
+      </c>
       <c r="I26">
-        <v>182</v>
+        <v>32.6</v>
       </c>
       <c r="J26">
-        <v>6.9</v>
+        <v>115</v>
       </c>
       <c r="K26">
-        <v>230</v>
+        <v>39.9</v>
       </c>
       <c r="L26">
-        <v>32.6</v>
+        <v>6.1</v>
       </c>
       <c r="M26">
-        <v>115</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="N26">
-        <v>39.9</v>
+        <v>1.23</v>
       </c>
       <c r="O26">
-        <v>6.1</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="P26">
-        <v>17.600000000000001</v>
+        <v>19.489000000000001</v>
       </c>
       <c r="Q26">
-        <v>1.23</v>
+        <v>146.4</v>
       </c>
       <c r="R26">
-        <v>0.17199999999999999</v>
+        <v>2.0110000000000001</v>
       </c>
       <c r="S26">
-        <v>19.489000000000001</v>
+        <v>1.903</v>
       </c>
       <c r="T26">
-        <v>146.4</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U26">
-        <v>2.0110000000000001</v>
+        <v>-4.17</v>
       </c>
       <c r="V26">
-        <v>1.903</v>
-      </c>
-      <c r="W26">
-        <v>-4.17</v>
-      </c>
-      <c r="X26">
         <v>-21.5</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="2">
+        <v>28</v>
+      </c>
+      <c r="D27">
         <v>-0.98819999999999997</v>
       </c>
-      <c r="H27" s="3">
+      <c r="E27">
         <v>10.9856</v>
       </c>
+      <c r="F27">
+        <v>215</v>
+      </c>
+      <c r="G27">
+        <v>7.3</v>
+      </c>
+      <c r="H27">
+        <v>327</v>
+      </c>
       <c r="I27">
-        <v>215</v>
+        <v>32.6</v>
       </c>
       <c r="J27">
-        <v>7.3</v>
+        <v>163</v>
       </c>
       <c r="K27">
-        <v>327</v>
+        <v>61.9</v>
       </c>
       <c r="L27">
-        <v>32.6</v>
+        <v>1.3</v>
       </c>
       <c r="M27">
-        <v>163</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="N27">
-        <v>61.9</v>
+        <v>1.98</v>
       </c>
       <c r="O27">
-        <v>1.3</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="P27">
-        <v>35.200000000000003</v>
+        <v>5.4779999999999998</v>
       </c>
       <c r="Q27">
-        <v>1.98</v>
+        <v>273.27999999999997</v>
       </c>
       <c r="R27">
-        <v>0.55700000000000005</v>
+        <v>19.454000000000001</v>
       </c>
       <c r="S27">
-        <v>5.4779999999999998</v>
+        <v>2.23</v>
       </c>
       <c r="T27">
-        <v>273.27999999999997</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U27">
-        <v>19.454000000000001</v>
+        <v>-3.56</v>
       </c>
       <c r="V27">
-        <v>2.23</v>
-      </c>
-      <c r="W27">
-        <v>-3.56</v>
-      </c>
-      <c r="X27">
         <v>-18.2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>34</v>
       </c>
       <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28">
+        <v>-0.98574799999999996</v>
+      </c>
+      <c r="E28">
+        <v>10.989000000000001</v>
+      </c>
+      <c r="F28">
+        <v>215</v>
+      </c>
+      <c r="G28">
+        <v>7.1</v>
+      </c>
+      <c r="H28">
+        <v>335</v>
+      </c>
+      <c r="I28">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="J28">
+        <v>168</v>
+      </c>
+      <c r="K28">
         <v>39</v>
       </c>
-      <c r="C28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" s="2">
-        <v>-0.98574799999999996</v>
-      </c>
-      <c r="H28" s="3">
-        <v>10.989000000000001</v>
-      </c>
-      <c r="I28">
-        <v>215</v>
-      </c>
-      <c r="J28">
-        <v>7.1</v>
-      </c>
-      <c r="K28">
-        <v>335</v>
-      </c>
       <c r="L28">
-        <v>32.200000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="M28">
-        <v>168</v>
+        <v>30.4</v>
       </c>
       <c r="N28">
-        <v>39</v>
+        <v>2.36</v>
       </c>
       <c r="O28">
-        <v>2.8</v>
+        <v>0.185</v>
       </c>
       <c r="P28">
-        <v>30.4</v>
+        <v>5.367</v>
       </c>
       <c r="Q28">
-        <v>2.36</v>
+        <v>200.08</v>
       </c>
       <c r="R28">
-        <v>0.185</v>
+        <v>12.624000000000001</v>
       </c>
       <c r="S28">
-        <v>5.367</v>
+        <v>4.7750000000000004</v>
       </c>
       <c r="T28">
-        <v>200.08</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U28">
-        <v>12.624000000000001</v>
+        <v>-3.58</v>
       </c>
       <c r="V28">
-        <v>4.7750000000000004</v>
-      </c>
-      <c r="W28">
-        <v>-3.58</v>
-      </c>
-      <c r="X28">
         <v>-20.8</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="2">
+        <v>28</v>
+      </c>
+      <c r="D29">
         <v>-0.99199999999999999</v>
       </c>
-      <c r="H29" s="3">
+      <c r="E29">
         <v>10.99</v>
       </c>
+      <c r="F29">
+        <v>215</v>
+      </c>
+      <c r="G29">
+        <v>7.4</v>
+      </c>
+      <c r="H29">
+        <v>452</v>
+      </c>
       <c r="I29">
-        <v>215</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="J29">
-        <v>7.4</v>
+        <v>226</v>
       </c>
       <c r="K29">
-        <v>452</v>
+        <v>47.8</v>
       </c>
       <c r="L29">
-        <v>32.299999999999997</v>
+        <v>10.5</v>
       </c>
       <c r="M29">
-        <v>226</v>
+        <v>34.4</v>
       </c>
       <c r="N29">
-        <v>47.8</v>
+        <v>3.81</v>
       </c>
       <c r="O29">
-        <v>10.5</v>
+        <v>0.153</v>
       </c>
       <c r="P29">
-        <v>34.4</v>
+        <v>21.045999999999999</v>
       </c>
       <c r="Q29">
-        <v>3.81</v>
+        <v>244</v>
       </c>
       <c r="R29">
-        <v>0.153</v>
+        <v>2.0640000000000001</v>
       </c>
       <c r="S29">
-        <v>21.045999999999999</v>
+        <v>1.635</v>
       </c>
       <c r="T29">
-        <v>244</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U29">
-        <v>2.0640000000000001</v>
+        <v>-3.23</v>
       </c>
       <c r="V29">
-        <v>1.635</v>
-      </c>
-      <c r="W29">
-        <v>-3.23</v>
-      </c>
-      <c r="X29">
         <v>-19</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="2">
+        <v>23</v>
+      </c>
+      <c r="D30">
         <v>-0.99758000000000002</v>
       </c>
-      <c r="H30" s="3">
+      <c r="E30">
         <v>10.95579</v>
       </c>
+      <c r="F30">
+        <v>207</v>
+      </c>
+      <c r="G30">
+        <v>6.9</v>
+      </c>
+      <c r="H30">
+        <v>458</v>
+      </c>
       <c r="I30">
-        <v>207</v>
+        <v>31.3</v>
       </c>
       <c r="J30">
-        <v>6.9</v>
+        <v>229</v>
       </c>
       <c r="K30">
-        <v>458</v>
+        <v>62.8</v>
       </c>
       <c r="L30">
-        <v>31.3</v>
+        <v>9.1</v>
       </c>
       <c r="M30">
-        <v>229</v>
+        <v>42.4</v>
       </c>
       <c r="N30">
-        <v>62.8</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="O30">
-        <v>9.1</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="P30">
-        <v>42.4</v>
+        <v>33.262999999999998</v>
       </c>
       <c r="Q30">
-        <v>2.2000000000000002</v>
+        <v>270.83999999999997</v>
       </c>
       <c r="R30">
-        <v>0.54400000000000004</v>
+        <v>3.1E-2</v>
       </c>
       <c r="S30">
-        <v>33.262999999999998</v>
+        <v>3.4809999999999999</v>
       </c>
       <c r="T30">
-        <v>270.83999999999997</v>
+        <v>6.0750000000000005E-2</v>
       </c>
       <c r="U30">
-        <v>3.1E-2</v>
+        <v>-3.48</v>
       </c>
       <c r="V30">
-        <v>3.4809999999999999</v>
-      </c>
-      <c r="W30">
-        <v>-3.48</v>
-      </c>
-      <c r="X30">
         <v>-20.100000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="2">
+        <v>23</v>
+      </c>
+      <c r="D31">
         <v>-1.0081899999999999</v>
       </c>
-      <c r="H31" s="3">
+      <c r="E31">
         <v>10.959899999999999</v>
       </c>
+      <c r="F31">
+        <v>207</v>
+      </c>
+      <c r="G31">
+        <v>7.2</v>
+      </c>
+      <c r="H31">
+        <v>473</v>
+      </c>
       <c r="I31">
-        <v>207</v>
+        <v>30.4</v>
       </c>
       <c r="J31">
-        <v>7.2</v>
+        <v>237</v>
       </c>
       <c r="K31">
-        <v>473</v>
+        <v>73</v>
       </c>
       <c r="L31">
-        <v>30.4</v>
+        <v>10.9</v>
       </c>
       <c r="M31">
-        <v>237</v>
+        <v>38.4</v>
       </c>
       <c r="N31">
-        <v>73</v>
+        <v>2.23</v>
       </c>
       <c r="O31">
-        <v>10.9</v>
+        <v>0.66</v>
       </c>
       <c r="P31">
-        <v>38.4</v>
+        <v>8.2119999999999997</v>
       </c>
       <c r="Q31">
-        <v>2.23</v>
+        <v>331.84</v>
       </c>
       <c r="R31">
-        <v>0.66</v>
+        <v>9.5180000000000007</v>
       </c>
       <c r="S31">
-        <v>8.2119999999999997</v>
+        <v>9.31</v>
       </c>
       <c r="T31">
-        <v>331.84</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U31">
-        <v>9.5180000000000007</v>
+        <v>-3.56</v>
       </c>
       <c r="V31">
-        <v>9.31</v>
-      </c>
-      <c r="W31">
-        <v>-3.56</v>
-      </c>
-      <c r="X31">
         <v>-21.2</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" t="s">
-        <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" s="2">
+        <v>23</v>
+      </c>
+      <c r="D32">
         <v>-1.00926</v>
       </c>
-      <c r="H32" s="3">
+      <c r="E32">
         <v>10.952999999999999</v>
       </c>
+      <c r="F32">
+        <v>207</v>
+      </c>
+      <c r="G32">
+        <v>7</v>
+      </c>
+      <c r="H32">
+        <v>386</v>
+      </c>
       <c r="I32">
-        <v>207</v>
+        <v>31.2</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>193</v>
       </c>
       <c r="K32">
-        <v>386</v>
+        <v>56.6</v>
       </c>
       <c r="L32">
-        <v>31.2</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>193</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="N32">
-        <v>56.6</v>
-      </c>
-      <c r="O32">
-        <v>9</v>
+        <v>2.36</v>
+      </c>
+      <c r="O32" t="s">
+        <v>25</v>
       </c>
       <c r="P32">
-        <v>32.799999999999997</v>
+        <v>21.082999999999998</v>
       </c>
       <c r="Q32">
-        <v>2.36</v>
-      </c>
-      <c r="R32" t="s">
-        <v>35</v>
+        <v>239.12</v>
+      </c>
+      <c r="R32">
+        <v>2.2629999999999999</v>
       </c>
       <c r="S32">
-        <v>21.082999999999998</v>
+        <v>4.7110000000000003</v>
       </c>
       <c r="T32">
-        <v>239.12</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U32">
-        <v>2.2629999999999999</v>
+        <v>-3.82</v>
       </c>
       <c r="V32">
-        <v>4.7110000000000003</v>
-      </c>
-      <c r="W32">
-        <v>-3.82</v>
-      </c>
-      <c r="X32">
         <v>-21.6</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" t="s">
-        <v>66</v>
-      </c>
-      <c r="F33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" s="2">
+        <v>56</v>
+      </c>
+      <c r="D33">
         <v>-1.055623</v>
       </c>
-      <c r="H33" s="3">
+      <c r="E33">
         <v>10.922473</v>
       </c>
+      <c r="F33">
+        <v>217</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+      <c r="H33">
+        <v>348</v>
+      </c>
       <c r="I33">
-        <v>217</v>
+        <v>29.7</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>174</v>
       </c>
       <c r="K33">
-        <v>348</v>
+        <v>42.9</v>
       </c>
       <c r="L33">
-        <v>29.7</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="M33">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="N33">
-        <v>42.9</v>
+        <v>0.88</v>
       </c>
       <c r="O33">
-        <v>19.100000000000001</v>
+        <v>1.0389999999999999</v>
       </c>
       <c r="P33">
-        <v>36</v>
+        <v>43.048000000000002</v>
       </c>
       <c r="Q33">
-        <v>0.88</v>
+        <v>156.16</v>
       </c>
       <c r="R33">
-        <v>1.0389999999999999</v>
+        <v>1.321</v>
       </c>
       <c r="S33">
-        <v>43.048000000000002</v>
+        <v>3.9279999999999999</v>
       </c>
       <c r="T33">
-        <v>156.16</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U33">
-        <v>1.321</v>
+        <v>-3.59</v>
       </c>
       <c r="V33">
-        <v>3.9279999999999999</v>
-      </c>
-      <c r="W33">
-        <v>-3.59</v>
-      </c>
-      <c r="X33">
         <v>-16.55</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="2">
+        <v>15</v>
+      </c>
+      <c r="D34">
         <v>-0.98599999999999999</v>
       </c>
-      <c r="H34" s="3">
+      <c r="E34">
         <v>10.923920000000001</v>
       </c>
+      <c r="F34">
+        <v>193</v>
+      </c>
+      <c r="G34">
+        <v>6.8</v>
+      </c>
+      <c r="H34">
+        <v>679</v>
+      </c>
       <c r="I34">
-        <v>193</v>
+        <v>32.4</v>
       </c>
       <c r="J34">
-        <v>6.8</v>
+        <v>340</v>
       </c>
       <c r="K34">
-        <v>679</v>
+        <v>97.3</v>
       </c>
       <c r="L34">
-        <v>32.4</v>
+        <v>13.1</v>
       </c>
       <c r="M34">
-        <v>340</v>
+        <v>52.8</v>
       </c>
       <c r="N34">
-        <v>97.3</v>
+        <v>3.84</v>
       </c>
       <c r="O34">
-        <v>13.1</v>
+        <v>1.294</v>
       </c>
       <c r="P34">
-        <v>52.8</v>
+        <v>34.029000000000003</v>
       </c>
       <c r="Q34">
-        <v>3.84</v>
+        <v>409.92</v>
       </c>
       <c r="R34">
-        <v>1.294</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="S34">
-        <v>34.029000000000003</v>
+        <v>3.2050000000000001</v>
       </c>
       <c r="T34">
-        <v>409.92</v>
+        <v>0.43274999999999997</v>
       </c>
       <c r="U34">
-        <v>0.54900000000000004</v>
+        <v>-3.03</v>
       </c>
       <c r="V34">
-        <v>3.2050000000000001</v>
-      </c>
-      <c r="W34">
-        <v>-3.03</v>
-      </c>
-      <c r="X34">
         <v>-19.399999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>43</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="2">
+        <v>15</v>
+      </c>
+      <c r="D35">
         <v>-0.98380000000000001</v>
       </c>
-      <c r="H35" s="3">
+      <c r="E35">
         <v>10.92245</v>
       </c>
+      <c r="F35">
+        <v>193</v>
+      </c>
+      <c r="G35">
+        <v>6.9</v>
+      </c>
+      <c r="H35">
+        <v>470</v>
+      </c>
       <c r="I35">
-        <v>193</v>
+        <v>32.1</v>
       </c>
       <c r="J35">
-        <v>6.9</v>
+        <v>235</v>
       </c>
       <c r="K35">
-        <v>470</v>
+        <v>62.6</v>
       </c>
       <c r="L35">
-        <v>32.1</v>
+        <v>8.1</v>
       </c>
       <c r="M35">
-        <v>235</v>
+        <v>34.4</v>
       </c>
       <c r="N35">
-        <v>62.6</v>
+        <v>3.82</v>
       </c>
       <c r="O35">
-        <v>8.1</v>
+        <v>2.391</v>
       </c>
       <c r="P35">
-        <v>34.4</v>
+        <v>15.356999999999999</v>
       </c>
       <c r="Q35">
-        <v>3.82</v>
+        <v>268.39999999999998</v>
       </c>
       <c r="R35">
-        <v>2.391</v>
+        <v>26.234000000000002</v>
       </c>
       <c r="S35">
-        <v>15.356999999999999</v>
+        <v>6.4880000000000004</v>
       </c>
       <c r="T35">
-        <v>268.39999999999998</v>
+        <v>0.51450000000000007</v>
       </c>
       <c r="U35">
-        <v>26.234000000000002</v>
+        <v>-2.54</v>
       </c>
       <c r="V35">
-        <v>6.4880000000000004</v>
-      </c>
-      <c r="W35">
-        <v>-2.54</v>
-      </c>
-      <c r="X35">
         <v>-16.2</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>44</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="2">
+        <v>15</v>
+      </c>
+      <c r="D36">
         <v>-0.97641999999999995</v>
       </c>
-      <c r="H36" s="3">
+      <c r="E36">
         <v>10.924894</v>
       </c>
+      <c r="F36">
+        <v>193</v>
+      </c>
+      <c r="G36">
+        <v>7.1</v>
+      </c>
+      <c r="H36">
+        <v>426</v>
+      </c>
       <c r="I36">
-        <v>193</v>
+        <v>32.6</v>
       </c>
       <c r="J36">
-        <v>7.1</v>
+        <v>213</v>
       </c>
       <c r="K36">
-        <v>426</v>
+        <v>115.9</v>
       </c>
       <c r="L36">
-        <v>32.6</v>
+        <v>10.3</v>
       </c>
       <c r="M36">
-        <v>213</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="N36">
-        <v>115.9</v>
+        <v>3.01</v>
       </c>
       <c r="O36">
-        <v>10.3</v>
+        <v>0.11</v>
       </c>
       <c r="P36">
-        <v>35.200000000000003</v>
+        <v>29.843</v>
       </c>
       <c r="Q36">
-        <v>3.01</v>
+        <v>370.88</v>
       </c>
       <c r="R36">
-        <v>0.11</v>
+        <v>6.9429999999999996</v>
       </c>
       <c r="S36">
-        <v>29.843</v>
+        <v>7.04</v>
       </c>
       <c r="T36">
-        <v>370.88</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U36">
-        <v>6.9429999999999996</v>
+        <v>-3.15</v>
       </c>
       <c r="V36">
-        <v>7.04</v>
-      </c>
-      <c r="W36">
-        <v>-3.15</v>
-      </c>
-      <c r="X36">
         <v>-22.05</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
-      </c>
-      <c r="D37" t="s">
-        <v>19</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="2">
+        <v>15</v>
+      </c>
+      <c r="D37">
         <v>-0.97587999999999997</v>
       </c>
-      <c r="H37" s="3">
+      <c r="E37">
         <v>10.928855</v>
       </c>
+      <c r="F37">
+        <v>193</v>
+      </c>
+      <c r="G37">
+        <v>6.9</v>
+      </c>
+      <c r="H37">
+        <v>472</v>
+      </c>
       <c r="I37">
-        <v>193</v>
+        <v>32.4</v>
       </c>
       <c r="J37">
-        <v>6.9</v>
+        <v>236</v>
       </c>
       <c r="K37">
-        <v>472</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="L37">
-        <v>32.4</v>
+        <v>5.8</v>
       </c>
       <c r="M37">
-        <v>236</v>
+        <v>33.6</v>
       </c>
       <c r="N37">
-        <v>65.900000000000006</v>
+        <v>3.4</v>
       </c>
       <c r="O37">
-        <v>5.8</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="P37">
-        <v>33.6</v>
+        <v>9.077</v>
       </c>
       <c r="Q37">
-        <v>3.4</v>
+        <v>278.16000000000003</v>
       </c>
       <c r="R37">
-        <v>0.13400000000000001</v>
+        <v>7.149</v>
       </c>
       <c r="S37">
-        <v>9.077</v>
+        <v>2.13</v>
       </c>
       <c r="T37">
-        <v>278.16000000000003</v>
+        <v>0.48449999999999999</v>
       </c>
       <c r="U37">
-        <v>7.149</v>
+        <v>-2.15</v>
       </c>
       <c r="V37">
-        <v>2.13</v>
-      </c>
-      <c r="W37">
-        <v>-2.15</v>
-      </c>
-      <c r="X37">
         <v>-15.2</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>46</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="2">
+        <v>15</v>
+      </c>
+      <c r="D38">
         <v>-0.97419999999999995</v>
       </c>
-      <c r="H38" s="3">
+      <c r="E38">
         <v>10.93211</v>
       </c>
+      <c r="F38">
+        <v>193</v>
+      </c>
+      <c r="G38">
+        <v>6.8</v>
+      </c>
+      <c r="H38">
+        <v>511</v>
+      </c>
       <c r="I38">
-        <v>193</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="J38">
+        <v>255</v>
+      </c>
+      <c r="K38">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="L38">
         <v>6.8</v>
       </c>
-      <c r="K38">
-        <v>511</v>
-      </c>
-      <c r="L38">
-        <v>32.200000000000003</v>
-      </c>
       <c r="M38">
-        <v>255</v>
+        <v>43.2</v>
       </c>
       <c r="N38">
-        <v>71.900000000000006</v>
+        <v>2.94</v>
       </c>
       <c r="O38">
-        <v>6.8</v>
+        <v>0.182</v>
       </c>
       <c r="P38">
-        <v>43.2</v>
+        <v>28.094000000000001</v>
       </c>
       <c r="Q38">
-        <v>2.94</v>
+        <v>287.92</v>
       </c>
       <c r="R38">
-        <v>0.182</v>
+        <v>2.0489999999999999</v>
       </c>
       <c r="S38">
-        <v>28.094000000000001</v>
+        <v>2.4380000000000002</v>
       </c>
       <c r="T38">
-        <v>287.92</v>
+        <v>0.58574999999999999</v>
       </c>
       <c r="U38">
-        <v>2.0489999999999999</v>
+        <v>-3.36</v>
       </c>
       <c r="V38">
-        <v>2.4380000000000002</v>
-      </c>
-      <c r="W38">
-        <v>-3.36</v>
-      </c>
-      <c r="X38">
         <v>-22.3</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" s="2">
+        <v>15</v>
+      </c>
+      <c r="D39">
         <v>-0.99138000000000004</v>
       </c>
-      <c r="H39" s="3">
+      <c r="E39">
         <v>10.91461</v>
       </c>
+      <c r="F39">
+        <v>193</v>
+      </c>
+      <c r="G39">
+        <v>6.8</v>
+      </c>
+      <c r="H39">
+        <v>464</v>
+      </c>
       <c r="I39">
-        <v>193</v>
+        <v>32.1</v>
       </c>
       <c r="J39">
-        <v>6.8</v>
+        <v>232</v>
       </c>
       <c r="K39">
-        <v>464</v>
+        <v>63.8</v>
       </c>
       <c r="L39">
-        <v>32.1</v>
+        <v>4.7</v>
       </c>
       <c r="M39">
-        <v>232</v>
+        <v>57.6</v>
       </c>
       <c r="N39">
-        <v>63.8</v>
+        <v>1.95</v>
       </c>
       <c r="O39">
-        <v>4.7</v>
+        <v>0.02</v>
       </c>
       <c r="P39">
-        <v>57.6</v>
+        <v>14.741</v>
       </c>
       <c r="Q39">
-        <v>1.95</v>
+        <v>336.72</v>
       </c>
       <c r="R39">
-        <v>0.02</v>
+        <v>33.183999999999997</v>
       </c>
       <c r="S39">
-        <v>14.741</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>336.72</v>
+        <v>0.51824999999999988</v>
       </c>
       <c r="U39">
-        <v>33.183999999999997</v>
+        <v>-3.38</v>
       </c>
       <c r="V39">
-        <v>1.39</v>
-      </c>
-      <c r="W39">
-        <v>-3.38</v>
-      </c>
-      <c r="X39">
         <v>-18.850000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D40" t="s">
-        <v>19</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="2">
+        <v>15</v>
+      </c>
+      <c r="D40">
         <v>-0.98960000000000004</v>
       </c>
-      <c r="H40" s="3">
+      <c r="E40">
         <v>10.912509999999999</v>
       </c>
+      <c r="F40">
+        <v>193</v>
+      </c>
+      <c r="G40">
+        <v>7</v>
+      </c>
+      <c r="H40">
+        <v>428</v>
+      </c>
       <c r="I40">
-        <v>193</v>
+        <v>32.6</v>
       </c>
       <c r="J40">
-        <v>7</v>
+        <v>215</v>
       </c>
       <c r="K40">
-        <v>428</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="L40">
-        <v>32.6</v>
+        <v>10.6</v>
       </c>
       <c r="M40">
-        <v>215</v>
+        <v>38.4</v>
       </c>
       <c r="N40">
-        <v>67.400000000000006</v>
+        <v>1.61</v>
       </c>
       <c r="O40">
-        <v>10.6</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="P40">
-        <v>38.4</v>
+        <v>18.902999999999999</v>
       </c>
       <c r="Q40">
-        <v>1.61</v>
+        <v>283.04000000000002</v>
       </c>
       <c r="R40">
-        <v>0.17199999999999999</v>
+        <v>31.94</v>
       </c>
       <c r="S40">
-        <v>18.902999999999999</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="T40">
-        <v>283.04000000000002</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U40">
-        <v>31.94</v>
+        <v>-2.63</v>
       </c>
       <c r="V40">
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="W40">
-        <v>-2.63</v>
-      </c>
-      <c r="X40">
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>49</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
-      </c>
-      <c r="D41" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="2">
+        <v>15</v>
+      </c>
+      <c r="D41">
         <v>-0.99502000000000002</v>
       </c>
-      <c r="H41" s="3">
+      <c r="E41">
         <v>10.909000000000001</v>
       </c>
+      <c r="F41">
+        <v>193</v>
+      </c>
+      <c r="G41">
+        <v>7.1</v>
+      </c>
+      <c r="H41">
+        <v>734</v>
+      </c>
       <c r="I41">
-        <v>193</v>
+        <v>32.6</v>
       </c>
       <c r="J41">
-        <v>7.1</v>
+        <v>368</v>
       </c>
       <c r="K41">
-        <v>734</v>
+        <v>119.2</v>
       </c>
       <c r="L41">
-        <v>32.6</v>
+        <v>15.1</v>
       </c>
       <c r="M41">
-        <v>368</v>
+        <v>44</v>
       </c>
       <c r="N41">
-        <v>119.2</v>
+        <v>3.94</v>
       </c>
       <c r="O41">
-        <v>15.1</v>
+        <v>1.32</v>
       </c>
       <c r="P41">
-        <v>44</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="Q41">
-        <v>3.94</v>
+        <v>488</v>
       </c>
       <c r="R41">
-        <v>1.32</v>
+        <v>38.854999999999997</v>
       </c>
       <c r="S41">
-        <v>0.63900000000000001</v>
+        <v>0.379</v>
       </c>
       <c r="T41">
-        <v>488</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U41">
-        <v>38.854999999999997</v>
+        <v>-3.75</v>
       </c>
       <c r="V41">
-        <v>0.379</v>
-      </c>
-      <c r="W41">
-        <v>-3.75</v>
-      </c>
-      <c r="X41">
         <v>-18.899999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
-      </c>
-      <c r="D42" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="2">
+        <v>15</v>
+      </c>
+      <c r="D42">
         <v>-0.99950000000000006</v>
       </c>
-      <c r="H42" s="3">
+      <c r="E42">
         <v>10.90422</v>
       </c>
+      <c r="F42">
+        <v>193</v>
+      </c>
+      <c r="G42">
+        <v>7.3</v>
+      </c>
+      <c r="H42">
+        <v>564</v>
+      </c>
       <c r="I42">
-        <v>193</v>
+        <v>32.5</v>
       </c>
       <c r="J42">
-        <v>7.3</v>
+        <v>283</v>
       </c>
       <c r="K42">
-        <v>564</v>
+        <v>82</v>
       </c>
       <c r="L42">
-        <v>32.5</v>
+        <v>10.6</v>
       </c>
       <c r="M42">
-        <v>283</v>
+        <v>21.6</v>
       </c>
       <c r="N42">
-        <v>82</v>
+        <v>3.64</v>
       </c>
       <c r="O42">
-        <v>10.6</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="P42">
-        <v>21.6</v>
+        <v>34.927</v>
       </c>
       <c r="Q42">
-        <v>3.64</v>
+        <v>258.64</v>
       </c>
       <c r="R42">
-        <v>0.13800000000000001</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="S42">
-        <v>34.927</v>
+        <v>1.5029999999999999</v>
       </c>
       <c r="T42">
-        <v>258.64</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="U42">
-        <v>0.38900000000000001</v>
+        <v>-4.08</v>
       </c>
       <c r="V42">
-        <v>1.5029999999999999</v>
-      </c>
-      <c r="W42">
-        <v>-4.08</v>
-      </c>
-      <c r="X42">
         <v>-22.5</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X42">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U42">
     <sortCondition ref="A2:A42"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
